--- a/litgraph/Lit_Review.xlsx
+++ b/litgraph/Lit_Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\Documents\GitHub\cxlso.github.io\litgraph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843A8645-498A-422A-AFD8-70BA5DBE1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155A8333-BB1C-41D1-A224-0D1E821DFC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" tabRatio="141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="606">
   <si>
     <t>ID</t>
   </si>
@@ -2052,6 +2052,23 @@
   </si>
   <si>
     <t>ICCC 25</t>
+  </si>
+  <si>
+    <t>Bratton, B. H. 2016</t>
+  </si>
+  <si>
+    <t>Bratton, B. H</t>
+  </si>
+  <si>
+    <t>The Stack: On Software and Sovereignty</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7551/mitpress/16135.001.0001</t>
+  </si>
+  <si>
+    <t>Bratton’s The Stack (2016) provides a critical framework for understanding planetary-scale computation as a layered geopolitical infrastructure. Drawing from the logic of protocol stacks, including the Open Systems Interconnection model, Bratton describes computation as a vertical system composed of Earth, Cloud, City, Address, Interface, and User. These layers organize the movement of matter, energy, data, identity, and control across contemporary technical systems. Computation is therefore not only a tool for representation or communication, but a spatial and political structure through which sovereignty is increasingly exercised.
+This layered model is especially relevant to open design and fabrication ecologies because it shows that data does not circulate freely or neutrally. It is routed, formatted, authenticated, captured, and governed through infrastructural layers: repositories, file formats, cloud platforms, machine protocols, user identities, and interfaces. In this sense, even open-source design workflows remain vulnerable to enclosure if the underlying stack is controlled by centralized platforms or opaque protocols.
+Read in relation to decentralized design-to-fabrication systems, Bratton’s work clarifies why openness must be infrastructural rather than merely file-based. Blockchain or distributed ledger systems can be understood as one possible response to this problem, particularly for managing authorship, versioning, provenance, and trust across distributed actors. However, their value depends on whether they support collective governance rather than new forms of extraction or speculation. Bratton therefore helps frame open design ecologies as questions of protocol sovereignty: how methods, data, and fabrication knowledge can circulate across interoperable layers while remaining legible, appropriable, and collectively governed.</t>
   </si>
 </sst>
 </file>
@@ -2121,12 +2138,16 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2432,13 +2453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.36328125" customWidth="1"/>
     <col min="2" max="2" width="76.90625" customWidth="1" outlineLevel="1"/>
     <col min="3" max="3" width="52.81640625" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="5" width="8.7265625" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="18" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="70.08984375" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="8.7265625" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="26.36328125" customWidth="1" outlineLevel="1"/>
@@ -4353,61 +4375,67 @@
         <v>545</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>601</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>602</v>
       </c>
       <c r="F68" t="s">
-        <v>301</v>
+        <v>603</v>
       </c>
       <c r="G68">
-        <v>2004</v>
-      </c>
-      <c r="J68" t="s">
-        <v>546</v>
+        <v>2016</v>
+      </c>
+      <c r="H68" t="s">
+        <v>360</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>439</v>
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
       </c>
       <c r="C69" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D69" t="s">
         <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>447</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G69">
-        <v>1803</v>
-      </c>
-      <c r="H69" t="s">
-        <v>377</v>
-      </c>
-      <c r="J69" t="s">
-        <v>547</v>
+        <v>2004</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>439</v>
       </c>
       <c r="C70" t="s">
         <v>592</v>
@@ -4416,21 +4444,24 @@
         <v>139</v>
       </c>
       <c r="E70" t="s">
-        <v>200</v>
+        <v>447</v>
       </c>
       <c r="F70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G70">
-        <v>1890</v>
+        <v>1803</v>
+      </c>
+      <c r="H70" t="s">
+        <v>377</v>
       </c>
       <c r="J70" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
         <v>592</v>
@@ -4439,21 +4470,21 @@
         <v>139</v>
       </c>
       <c r="E71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F71" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G71">
-        <v>1984</v>
+        <v>1890</v>
       </c>
       <c r="J71" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" t="s">
         <v>592</v>
@@ -4462,73 +4493,73 @@
         <v>139</v>
       </c>
       <c r="E72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F72" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G72">
-        <v>1987</v>
-      </c>
-      <c r="H72" t="s">
-        <v>378</v>
+        <v>1984</v>
       </c>
       <c r="J72" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D73" t="s">
         <v>139</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F73" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G73">
         <v>1987</v>
       </c>
+      <c r="H73" t="s">
+        <v>378</v>
+      </c>
       <c r="J73" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="B74" t="s">
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D74" t="s">
         <v>139</v>
       </c>
       <c r="E74" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G74">
-        <v>1993</v>
+        <v>1987</v>
       </c>
       <c r="J74" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
         <v>592</v>
@@ -4537,24 +4568,21 @@
         <v>139</v>
       </c>
       <c r="E75" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G75">
-        <v>1963</v>
+        <v>1993</v>
       </c>
       <c r="J75" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="C76" t="s">
         <v>592</v>
@@ -4563,21 +4591,24 @@
         <v>139</v>
       </c>
       <c r="E76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G76">
-        <v>1952</v>
+        <v>1963</v>
       </c>
       <c r="J76" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="B77" t="s">
+        <v>132</v>
       </c>
       <c r="C77" t="s">
         <v>592</v>
@@ -4586,67 +4617,67 @@
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F77" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G77">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="J77" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D78" t="s">
         <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F78" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G78">
-        <v>1961</v>
+        <v>1948</v>
       </c>
       <c r="J78" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D79" t="s">
         <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G79">
-        <v>1970</v>
+        <v>1961</v>
       </c>
       <c r="J79" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
         <v>592</v>
@@ -4655,114 +4686,108 @@
         <v>139</v>
       </c>
       <c r="E80" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G80">
-        <v>2002</v>
-      </c>
-      <c r="H80" t="s">
-        <v>379</v>
+        <v>1970</v>
       </c>
       <c r="J80" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D81" t="s">
         <v>139</v>
       </c>
       <c r="E81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F81" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G81">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="H81" t="s">
-        <v>459</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="J81" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>436</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G82">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="H82" t="s">
-        <v>380</v>
+        <v>459</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="J82" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="B83" t="s">
+        <v>436</v>
       </c>
       <c r="C83" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D83" t="s">
         <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F83" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G83">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H83" t="s">
-        <v>458</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>418</v>
+        <v>380</v>
       </c>
       <c r="J83" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C84" t="s">
         <v>590</v>
@@ -4771,59 +4796,59 @@
         <v>139</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F84" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G84">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="H84" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J84" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" t="s">
-        <v>430</v>
+        <v>88</v>
       </c>
       <c r="C85" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D85" t="s">
         <v>139</v>
       </c>
       <c r="E85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F85" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G85">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="H85" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J85" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="B86" t="s">
+        <v>430</v>
       </c>
       <c r="C86" t="s">
         <v>593</v>
@@ -4832,30 +4857,27 @@
         <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G86">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="H86" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J86" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="C87" t="s">
         <v>593</v>
@@ -4864,27 +4886,30 @@
         <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F87" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G87">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="H87" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J87" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="B88" t="s">
+        <v>134</v>
       </c>
       <c r="C88" t="s">
         <v>593</v>
@@ -4893,319 +4918,328 @@
         <v>139</v>
       </c>
       <c r="E88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F88" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G88">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="H88" t="s">
-        <v>381</v>
+        <v>454</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="J88" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D89" t="s">
         <v>139</v>
       </c>
       <c r="E89" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F89" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G89">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="H89" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="J89" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D90" t="s">
         <v>139</v>
       </c>
       <c r="E90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F90" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G90">
-        <v>2015</v>
+        <v>1993</v>
       </c>
       <c r="H90" t="s">
-        <v>449</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="J90" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D91" t="s">
         <v>139</v>
       </c>
       <c r="E91" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F91" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G91">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H91" t="s">
-        <v>382</v>
+        <v>449</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="J91" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D92" t="s">
         <v>139</v>
       </c>
       <c r="E92" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G92">
         <v>2014</v>
       </c>
       <c r="H92" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J92" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>97</v>
-      </c>
-      <c r="B93" t="s">
-        <v>431</v>
+        <v>96</v>
       </c>
       <c r="C93" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D93" t="s">
         <v>139</v>
       </c>
       <c r="E93" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="F93" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G93">
-        <v>1963</v>
+        <v>2014</v>
       </c>
       <c r="H93" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J93" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="B94" t="s">
+        <v>431</v>
       </c>
       <c r="C94" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D94" t="s">
         <v>139</v>
       </c>
       <c r="E94" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G94">
-        <v>2020</v>
+        <v>1963</v>
       </c>
       <c r="H94" t="s">
-        <v>452</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>424</v>
+        <v>384</v>
       </c>
       <c r="J94" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F95" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G95">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="H95" t="s">
-        <v>385</v>
+        <v>452</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="J95" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C96" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D96" t="s">
         <v>139</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F96" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G96">
-        <v>1951</v>
+        <v>2011</v>
+      </c>
+      <c r="H96" t="s">
+        <v>385</v>
       </c>
       <c r="J96" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D97" t="s">
         <v>139</v>
       </c>
       <c r="E97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G97">
-        <v>2019</v>
-      </c>
-      <c r="H97" t="s">
-        <v>451</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>386</v>
+        <v>1951</v>
       </c>
       <c r="J97" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C98" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D98" t="s">
         <v>139</v>
       </c>
       <c r="E98" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G98">
         <v>2019</v>
       </c>
       <c r="H98" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J98" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>103</v>
-      </c>
-      <c r="B99" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C99" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E99" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="F99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G99">
-        <v>1949</v>
+        <v>2019</v>
+      </c>
+      <c r="H99" t="s">
+        <v>450</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J99" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="B100" t="s">
+        <v>135</v>
       </c>
       <c r="C100" t="s">
         <v>591</v>
@@ -5214,18 +5248,18 @@
         <v>140</v>
       </c>
       <c r="E100" t="s">
-        <v>228</v>
+        <v>149</v>
       </c>
       <c r="F100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G100">
-        <v>1776</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s">
         <v>591</v>
@@ -5234,21 +5268,18 @@
         <v>140</v>
       </c>
       <c r="E101" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F101" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G101">
-        <v>1848</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>106</v>
-      </c>
-      <c r="B102" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C102" t="s">
         <v>591</v>
@@ -5257,18 +5288,21 @@
         <v>140</v>
       </c>
       <c r="E102" t="s">
-        <v>148</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G102">
-        <v>1962</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="B103" t="s">
+        <v>136</v>
       </c>
       <c r="C103" t="s">
         <v>591</v>
@@ -5277,18 +5311,18 @@
         <v>140</v>
       </c>
       <c r="E103" t="s">
-        <v>230</v>
+        <v>148</v>
       </c>
       <c r="F103" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G103">
-        <v>1949</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C104" t="s">
         <v>591</v>
@@ -5297,116 +5331,113 @@
         <v>140</v>
       </c>
       <c r="E104" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F104" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G104">
-        <v>1962</v>
-      </c>
-      <c r="H104" t="s">
-        <v>388</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C105" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D105" t="s">
         <v>140</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F105" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G105">
-        <v>2021</v>
+        <v>1962</v>
       </c>
       <c r="H105" t="s">
-        <v>596</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C106" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D106" t="s">
         <v>140</v>
       </c>
       <c r="E106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G106">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H106" t="s">
-        <v>390</v>
+        <v>596</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C107" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D107" t="s">
         <v>140</v>
       </c>
       <c r="E107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G107">
-        <v>1975</v>
+        <v>2023</v>
       </c>
       <c r="H107" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C108" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D108" t="s">
         <v>140</v>
       </c>
       <c r="E108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F108" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G108">
-        <v>1902</v>
+        <v>1975</v>
+      </c>
+      <c r="H108" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>113</v>
-      </c>
-      <c r="B109" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
         <v>592</v>
@@ -5415,18 +5446,21 @@
         <v>140</v>
       </c>
       <c r="E109" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="F109" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G109">
-        <v>1936</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="B110" t="s">
+        <v>137</v>
       </c>
       <c r="C110" t="s">
         <v>592</v>
@@ -5435,64 +5469,84 @@
         <v>140</v>
       </c>
       <c r="E110" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G110">
-        <v>1931</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>115</v>
-      </c>
-      <c r="B111" t="s">
-        <v>432</v>
+        <v>114</v>
       </c>
       <c r="C111" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D111" t="s">
         <v>140</v>
       </c>
       <c r="E111" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F111" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G111">
-        <v>2022</v>
-      </c>
-      <c r="H111" t="s">
-        <v>453</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>425</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
+      </c>
+      <c r="B112" t="s">
+        <v>432</v>
       </c>
       <c r="C112" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D112" t="s">
         <v>140</v>
       </c>
       <c r="E112" t="s">
+        <v>237</v>
+      </c>
+      <c r="F112" t="s">
+        <v>344</v>
+      </c>
+      <c r="G112">
+        <v>2022</v>
+      </c>
+      <c r="H112" t="s">
+        <v>453</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>116</v>
+      </c>
+      <c r="C113" t="s">
+        <v>592</v>
+      </c>
+      <c r="D113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E113" t="s">
         <v>238</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F113" t="s">
         <v>345</v>
       </c>
-      <c r="G112">
+      <c r="G113">
         <v>1966</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H113" t="s">
         <v>392</v>
       </c>
     </row>
@@ -5524,21 +5578,22 @@
     <hyperlink ref="I64" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
     <hyperlink ref="I65" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
     <hyperlink ref="I67" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="I81" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="I83" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="I84" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="I85" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="I86" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="I87" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="I90" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="I94" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="I97" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="I98" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="I105" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="I111" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="I82" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I84" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I85" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I86" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I87" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I88" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I91" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I95" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I98" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I99" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I106" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I112" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
     <hyperlink ref="I35" r:id="rId39" xr:uid="{E5F347C5-5D6B-4351-8E82-0C7763FF2326}"/>
     <hyperlink ref="I19" r:id="rId40" xr:uid="{174D6D23-9E65-4EE0-A27A-BE34DB0F421A}"/>
     <hyperlink ref="I66" r:id="rId41" xr:uid="{D30E4B2A-C639-4034-8270-0EF978D1B539}"/>
+    <hyperlink ref="I68" r:id="rId42" xr:uid="{E5FA7AD5-9540-4144-A1DF-E18F4F9B7B30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/litgraph/Lit_Review.xlsx
+++ b/litgraph/Lit_Review.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R891e1c6d2bd94223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56531659fcad4278"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3467,8 +3467,8 @@
         <x:v>https://doi.org/10.1515/9783035624373</x:v>
       </x:c>
       <x:c r="J100" t="str">
-        <x:v>APA citation: Allner, L., Kaltenbrunner, C., Kröhnert, D., &amp; Reinsberg, P. (Eds.). (2021). Conceptual Joining: Wood Structures from Detail to Utopia / Wood Structures in Experimentation. De Gruyter. https://doi.org/10.1515/9783035624373
-Conceptual Joining examines timber structures through the detail, treating joints not as neutral connections but as sites where material behavior, craft knowledge, structural logic, and architectural imagination meet. In relation to Post-Anthropogenic Design-to-Fabrication Practices Towards Global Symbiosis, the book strengthens the argument that design-to-fabrication is an ecological and relational continuum: wood, tools, assembly protocols, and speculative futures participate together in the production of tectonic knowledge. Its emphasis on experimentation helps frame Symbiotic Material Ecologies as practices that learn from material agency rather than simply imposing form.</x:v>
+        <x:v>Conceptual Joining examines timber architecture through the logic of the joint, treating connection details as generative sites where material behavior, structural reasoning, craft knowledge, and architectural imagination converge. Rather than presenting wood structures only as finished objects or formal compositions, the book follows the detail as a site of inquiry: how components meet, how forces are transferred, how tolerances and fabrication decisions shape assembly, and how tectonic thinking can move from precise construction knowledge toward speculative spatial possibilities. The subtitle's movement from detail to utopia is important, because it suggests that small-scale joining systems can carry larger architectural, ecological, and cultural ambitions.
+This makes the book especially relevant to Symbiotic Material Ecologies. Wood is not framed merely as a renewable material to be optimized, but as a medium with grain, anisotropy, growth history, structural limits, and expressive capacities that actively condition design decisions. Joining becomes a negotiation among material agency, fabrication technique, structural performance, and architectural intent. Read alongside a post-anthropogenic design-to-fabrication framework, the book helps shift attention from fabrication as the execution of a predefined form toward fabrication as a relational process, where materials, tools, assemblies, and environments participate in the production of tectonic knowledge.</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -3498,8 +3498,8 @@
         <x:v>https://openlibrary.org/isbn/9787560873343</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>APA citation: Yuan, P. F., Menges, A., &amp; Leach, N. (Eds.). (2018). Digital Fabrication. Tongji University Press Co., Ltd.
-Digital Fabrication gathers architectural approaches in which computational design, materialization, and fabrication research operate as a coupled process. For the dissertation, it is a useful secondary reference for Phygital Practices because it situates fabrication as a hybrid field between digital protocols and physical matter: robotic tools, machine logics, craft, material feedback, and design intelligence become mutually conditioning agents. Read alongside the dissertation’s post-anthropogenic agenda, the book helps trace how digital fabrication can move beyond efficient production toward distributed, experimental, and materially responsive design ecologies.</x:v>
+        <x:v>Digital Fabrication presents architectural production as a field in which computational design and physical making are directly intertwined. The book gathers approaches that connect geometry, code, machines, prototypes, and material behavior, showing how fabrication technologies reshape both the methods and the imagination of architectural practice. Its focus is not fabrication as the final translation of a digital model, but fabrication as an experimental design medium in its own right, where CNC processes, robotic systems, additive and subtractive techniques, material constraints, and iterative prototyping all feed back into the development of form, structure, and spatial logic.
+The book is a strong reference for Phygital Practices because it clarifies how digital protocols and material realities co-produce architectural knowledge. Machine operations are not treated as neutral tools; they become part of a wider feedback loop among software, hardware, material response, and design intention. This is useful for understanding the transition from representation-based design toward fabrication-aware design cultures, where computation is tested through matter and matter, in turn, redirects computation. Within a post-anthropogenic design-to-fabrication argument, the book also marks a necessary step beyond technological novelty: digital fabrication becomes a platform for distributed, adaptive, and materially responsive systems rather than only a means of efficient production.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -3864,48 +3864,48 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="R8cb2401017824f80"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="Rb1fd125d87904de8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="R4a4717a13d024e49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="Recedd76fb5e440bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="R0453d4fe730742b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="Rebbf44bc51e54082"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R06fa1f94825740a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="Ra628dbc50c264cb5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R1e25037627244342"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="R9250d13ee3df4081"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="R759133aa62894b1a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="Rc5cd1b81621e4154"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="Rf4e969f30b1b4278"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="R1d7b694e9e4d46c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="R812ce047a86f4842"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="Rdbd387fdb9e34129"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="Rfbbb44ffd58b4d38"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="R9b54fc4a6ff64144"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="Rb1e4019d0e9f494f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="R74758cb27e224bfc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="R2b04d5447bbb4aa9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="Ra3870eb6c9dc46fa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="R704f598f1e9540ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="Red94e079b3fd434f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="R4acf49e5902d43f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="R03301d8623cf4838"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="R49e1cd646b374b34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="R469cf05d36a846c7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="R523f40eb647b4e17"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="R2e2b11d9929c4a4a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="Rff5a04cde53d4a19"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="R88ddb5306b1b4d26"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="R944803cc43dd4519"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="Re4ab376e50964517"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="R33967753776645b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="R1529c21d53084870"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="Rd259a95f2440431e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="R250c4251ed4b4f21"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="R1ae3956c26414dbd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="Rc2f86e3b6be0439b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="Rdabc700f8e8c4ca8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="R253acbe854744acd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="Ref85c1aa3f3e4d6c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="Re7ccad79c8014d0e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="R21368b1edafa4b2b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="R22a65af56a194012"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="R618c99386dfa4681"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="Rd29de5f49a30402c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="R3421dd09f88047bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="R637793fda7d449f2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="R309899d8b67047ec"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="R5562164071b2419e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="Red236e8be8404858"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="R047ad6a9a8ab49e8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="R507da883d93c4ba2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="R541d165054b44e6c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="R7f3fdb89ebb94efe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="R5a498b052dde458b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="R822ada1529644954"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="Ra8e856331b5d4aef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="R478af8bfb25542c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="R7372f01c6f4643ff"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="R9b3d8c8a0f9744d8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="R637e3dbd5f2f48d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="R9d9abed46f914167"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="R7d844139235e4d84"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="Rd92258952fdf40cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="Rfa41c41e8fa04a45"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="R4cb6c779f0244d28"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="Rbb29753632ce4750"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="Re547a8998226471d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="R1f47c0500bde4a50"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="R53b68afb3a2142a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="R7860eedaf24d4723"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="R4b97a7ab23bd4794"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="Rd208d0feab3b4d6c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="Rfeed9117fcdb4826"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="R44775ae0cc1f4e01"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="R2d79037d37124dc8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="R09093cdcb24c49ca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="R604ace63ded54122"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="R8c5ac5b25b064ea3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="R50234e710d1c4117"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="Rb582e3fdebc041d4"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
